--- a/event_feedback_forms/007_zoom_event_feedback_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/007_zoom_event_feedback_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,8 +926,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -955,12 +955,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'highly_satisfied',_'value':_5}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Satisfied', 'value': 5}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_3}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 3}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_2}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': 2}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied',_'value':_1}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied', 'value': 1}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_10',_'value':_10}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 10', 'value': 10}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'10-20',_'value':_20}</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '10-20', 'value': 20}</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'20-50',_'value':_50}</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '20-50', 'value': 50}</t>
+          <t>20-50</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'50_or_more',_'value':_50}</t>
+          <t>50_or_more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '50 or more', 'value': 50}</t>
+          <t>50 or more</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'English', 'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish', 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'french',_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'French', 'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'utc+0',_'value':_'utc+0'}</t>
+          <t>utc+0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'UTC+0', 'value': 'UTC+0'}</t>
+          <t>UTC+0</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'utc-8',_'value':_'utc-8'}</t>
+          <t>utc-8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'UTC-8', 'value': 'UTC-8'}</t>
+          <t>UTC-8</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'utc+8',_'value':_'utc+8'}</t>
+          <t>utc+8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'UTC+8', 'value': 'UTC+8'}</t>
+          <t>UTC+8</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
